--- a/metadata/trials-metadata/aannotators-leaders/authors-metadata.xlsx
+++ b/metadata/trials-metadata/aannotators-leaders/authors-metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-data/metadata/trials-metadata/annotators-leaders/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-data/metadata/trials-metadata/aannotators-leaders/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04337F04-1174-E540-96D2-B0AB3CF7A0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A19035-F7A9-764C-9205-2B596634F3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32260" yWindow="2280" windowWidth="30720" windowHeight="19200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1720" yWindow="500" windowWidth="30720" windowHeight="19200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="authors" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="117">
   <si>
     <t>given_name</t>
   </si>
@@ -366,6 +366,18 @@
   <si>
     <t>Dorado-Betancourt</t>
   </si>
+  <si>
+    <t>Marilyn</t>
+  </si>
+  <si>
+    <t>Allan</t>
+  </si>
+  <si>
+    <t>Coto</t>
+  </si>
+  <si>
+    <t>Manrow-Villalobos</t>
+  </si>
 </sst>
 </file>
 
@@ -696,11 +708,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA1002"/>
+  <dimension ref="A1:AA1004"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.33203125" customWidth="1"/>
     <col min="4" max="4" width="22.5" customWidth="1"/>
     <col min="5" max="5" width="35.5" customWidth="1"/>
@@ -1078,19 +1090,16 @@
     </row>
     <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -1117,19 +1126,16 @@
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -1156,16 +1162,19 @@
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>81</v>
+      </c>
+      <c r="C12" t="s">
+        <v>82</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -1192,13 +1201,13 @@
     </row>
     <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
@@ -1231,16 +1240,13 @@
     </row>
     <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
@@ -1270,19 +1276,19 @@
     </row>
     <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -1309,19 +1315,19 @@
     </row>
     <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -1348,19 +1354,19 @@
     </row>
     <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B17" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -1387,19 +1393,19 @@
     </row>
     <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
         <v>31</v>
       </c>
       <c r="E18" t="s">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -1426,16 +1432,16 @@
     </row>
     <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="s">
         <v>56</v>
@@ -1464,11 +1470,21 @@
       <c r="AA19" s="2"/>
     </row>
     <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="2"/>
+      <c r="A20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" t="s">
+        <v>106</v>
+      </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -1493,11 +1509,21 @@
       <c r="AA20" s="2"/>
     </row>
     <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="2"/>
+      <c r="A21" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" t="s">
+        <v>56</v>
+      </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -1555,7 +1581,7 @@
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
+      <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -1584,7 +1610,7 @@
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
+      <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -1642,7 +1668,7 @@
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="2"/>
+      <c r="E26" s="3"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -1671,7 +1697,7 @@
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="3"/>
-      <c r="E27" s="2"/>
+      <c r="E27" s="3"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -2221,7 +2247,7 @@
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
+      <c r="D46" s="3"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
@@ -2250,7 +2276,7 @@
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
+      <c r="D47" s="3"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
@@ -29970,6 +29996,64 @@
       <c r="Z1002" s="2"/>
       <c r="AA1002" s="2"/>
     </row>
+    <row r="1003" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1003" s="2"/>
+      <c r="B1003" s="2"/>
+      <c r="C1003" s="2"/>
+      <c r="D1003" s="2"/>
+      <c r="E1003" s="2"/>
+      <c r="F1003" s="2"/>
+      <c r="G1003" s="2"/>
+      <c r="H1003" s="2"/>
+      <c r="I1003" s="2"/>
+      <c r="J1003" s="2"/>
+      <c r="K1003" s="2"/>
+      <c r="L1003" s="2"/>
+      <c r="M1003" s="2"/>
+      <c r="N1003" s="2"/>
+      <c r="O1003" s="2"/>
+      <c r="P1003" s="2"/>
+      <c r="Q1003" s="2"/>
+      <c r="R1003" s="2"/>
+      <c r="S1003" s="2"/>
+      <c r="T1003" s="2"/>
+      <c r="U1003" s="2"/>
+      <c r="V1003" s="2"/>
+      <c r="W1003" s="2"/>
+      <c r="X1003" s="2"/>
+      <c r="Y1003" s="2"/>
+      <c r="Z1003" s="2"/>
+      <c r="AA1003" s="2"/>
+    </row>
+    <row r="1004" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1004" s="2"/>
+      <c r="B1004" s="2"/>
+      <c r="C1004" s="2"/>
+      <c r="D1004" s="2"/>
+      <c r="E1004" s="2"/>
+      <c r="F1004" s="2"/>
+      <c r="G1004" s="2"/>
+      <c r="H1004" s="2"/>
+      <c r="I1004" s="2"/>
+      <c r="J1004" s="2"/>
+      <c r="K1004" s="2"/>
+      <c r="L1004" s="2"/>
+      <c r="M1004" s="2"/>
+      <c r="N1004" s="2"/>
+      <c r="O1004" s="2"/>
+      <c r="P1004" s="2"/>
+      <c r="Q1004" s="2"/>
+      <c r="R1004" s="2"/>
+      <c r="S1004" s="2"/>
+      <c r="T1004" s="2"/>
+      <c r="U1004" s="2"/>
+      <c r="V1004" s="2"/>
+      <c r="W1004" s="2"/>
+      <c r="X1004" s="2"/>
+      <c r="Y1004" s="2"/>
+      <c r="Z1004" s="2"/>
+      <c r="AA1004" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -29980,7 +30064,7 @@
           <x14:formula1>
             <xm:f>roles_options!$A$2:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D45</xm:sqref>
+          <xm:sqref>D2:D47</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
